--- a/Data Analysis/LW6/iris.xlsx
+++ b/Data Analysis/LW6/iris.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\studies\Data Analysis\LW6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1B9403-2584-4C56-ADDE-23E08068F052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0740153-007B-498F-8B94-CF55CBA70DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -256,70 +256,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9" tint="0.79998168889431442"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9" tint="0.79998168889431442"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -514,13 +465,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="9" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="9" tint="0.39997558519241921"/>
         </left>
@@ -534,6 +478,62 @@
           <color theme="9" tint="0.39997558519241921"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="9" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4630,14 +4630,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F0D1B16A-0315-47E3-8AE3-9C1BC0F07A2C}" name="Таблица4" displayName="Таблица4" ref="B1:F151" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F0D1B16A-0315-47E3-8AE3-9C1BC0F07A2C}" name="Таблица4" displayName="Таблица4" ref="B1:F151" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="B1:F151" xr:uid="{F0D1B16A-0315-47E3-8AE3-9C1BC0F07A2C}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B05A2E13-DA99-4D05-8733-60236F3A63F2}" name="sepal_length" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{59AECCBB-A674-4BE1-8FC2-A3C76DA9259E}" name="sepal_width" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{4BE11A76-58DE-42B3-8AC3-1F20659798C9}" name="petal_length" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{A5088A7E-5A66-4EB1-AC79-137C9B587433}" name="petal_width" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{31D7E34D-4D42-409C-A810-6173C273B345}" name="species" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{B05A2E13-DA99-4D05-8733-60236F3A63F2}" name="sepal_length" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{59AECCBB-A674-4BE1-8FC2-A3C76DA9259E}" name="sepal_width" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{4BE11A76-58DE-42B3-8AC3-1F20659798C9}" name="petal_length" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{A5088A7E-5A66-4EB1-AC79-137C9B587433}" name="petal_width" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{31D7E34D-4D42-409C-A810-6173C273B345}" name="species" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4722,6 +4722,21 @@
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{076C5541-447B-4019-A679-2A4AB9C37794}" name="Расстояние"/>
     <tableColumn id="2" xr3:uid="{B0CE9AAF-B9BD-4318-834A-08F1FDA4F8C8}" name="Класс"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A67C7A5C-92BE-4DD0-9E7C-F4E4BC0D6E98}" name="Таблица1" displayName="Таблица1" ref="M31:N45" totalsRowShown="0">
+  <autoFilter ref="M31:N45" xr:uid="{A67C7A5C-92BE-4DD0-9E7C-F4E4BC0D6E98}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{C9E79229-4D73-47CE-9306-BC2BE44B8A78}" name="Расстояние">
+      <calculatedColumnFormula>SQRT(($N$21 - N3)^2 + ($O$21 - O3)^2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{0A78D384-8251-4491-B9FD-848CF5F7614B}" name="Класс">
+      <calculatedColumnFormula>P3</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5000,7 +5015,7 @@
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
     <col min="14" max="14" width="12.42578125" customWidth="1"/>
     <col min="16" max="16" width="13.42578125" customWidth="1"/>
   </cols>
@@ -5030,12 +5045,12 @@
       <c r="K1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B2" s="3">
@@ -5684,12 +5699,12 @@
       <c r="K19" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="M19" s="10" t="s">
+      <c r="M19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
@@ -6034,10 +6049,10 @@
       <c r="K29" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B30" s="3">
@@ -6068,10 +6083,10 @@
         <v>14</v>
       </c>
       <c r="V30" s="9"/>
-      <c r="W30" s="11"/>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="11"/>
-      <c r="Z30" s="11"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="10"/>
     </row>
     <row r="31" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
@@ -6116,7 +6131,7 @@
       <c r="T31" t="s">
         <v>13</v>
       </c>
-      <c r="V31" s="13" t="s">
+      <c r="V31" s="11" t="s">
         <v>11</v>
       </c>
       <c r="X31" t="s">
@@ -6128,10 +6143,10 @@
       <c r="Z31" t="s">
         <v>27</v>
       </c>
-      <c r="AA31" s="13" t="s">
+      <c r="AA31" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AB31" s="13" t="s">
+      <c r="AB31" s="11" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6180,7 +6195,7 @@
       <c r="T32" t="s">
         <v>5</v>
       </c>
-      <c r="V32" s="13"/>
+      <c r="V32" s="11"/>
       <c r="W32" t="s">
         <v>22</v>
       </c>
@@ -6247,7 +6262,7 @@
       <c r="T33" t="s">
         <v>5</v>
       </c>
-      <c r="V33" s="13"/>
+      <c r="V33" s="11"/>
       <c r="W33" t="s">
         <v>23</v>
       </c>
@@ -6305,7 +6320,7 @@
       <c r="Q34" t="s">
         <v>5</v>
       </c>
-      <c r="V34" s="13"/>
+      <c r="V34" s="11"/>
       <c r="W34" t="s">
         <v>24</v>
       </c>
@@ -6443,7 +6458,7 @@
       <c r="Q37" t="s">
         <v>6</v>
       </c>
-      <c r="V37" s="13" t="s">
+      <c r="V37" s="11" t="s">
         <v>30</v>
       </c>
       <c r="X37" t="s">
@@ -6455,10 +6470,10 @@
       <c r="Z37" t="s">
         <v>27</v>
       </c>
-      <c r="AA37" s="13" t="s">
+      <c r="AA37" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AB37" s="13" t="s">
+      <c r="AB37" s="11" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6501,7 +6516,7 @@
       <c r="Q38" t="s">
         <v>6</v>
       </c>
-      <c r="V38" s="13"/>
+      <c r="V38" s="11"/>
       <c r="W38" t="s">
         <v>22</v>
       </c>
@@ -6562,7 +6577,7 @@
       <c r="Q39" t="s">
         <v>6</v>
       </c>
-      <c r="V39" s="13"/>
+      <c r="V39" s="11"/>
       <c r="W39" t="s">
         <v>23</v>
       </c>
@@ -6620,7 +6635,7 @@
       <c r="Q40" t="s">
         <v>6</v>
       </c>
-      <c r="V40" s="13"/>
+      <c r="V40" s="11"/>
       <c r="W40" t="s">
         <v>24</v>
       </c>
@@ -9023,7 +9038,7 @@
         <v>6</v>
       </c>
       <c r="M101">
-        <f t="shared" ref="M101:M113" si="10">SQRT(($N$25 - N4)^2 + ($O$25 - O4)^2)</f>
+        <f t="shared" ref="M101:M112" si="10">SQRT(($N$25 - N4)^2 + ($O$25 - O4)^2)</f>
         <v>4.6097722286464435</v>
       </c>
       <c r="N101" t="str">
@@ -10749,7 +10764,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <tableParts count="7">
+  <tableParts count="8">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
@@ -10757,6 +10772,7 @@
     <tablePart r:id="rId6"/>
     <tablePart r:id="rId7"/>
     <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
